--- a/forms/trg/Formulir_TRG_mcrg.xlsx
+++ b/forms/trg/Formulir_TRG_mcrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B50)</f>
+        <f>COUNTA(Anggota!B5:B51)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F50)</f>
+        <f>COUNTA(Anggota!F5:F51)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Filsah Muslimat, S.S., S.Pd., M. Hum.</t>
+          <t>Prof. Dr. Muhlis Hadrawi, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Mandarin Language and Chinese Culture</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Linguistics</t>
+          <t>Specialist in Philological Studies</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0852-8080</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6024282</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57193015650</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,38 +958,30 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nurhayati Rahman, MS.</t>
+          <t>Andi Filsah Muslimat, S.S., S.Pd., M. Hum.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of Mandarin Language and Chinese Culture</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Philological Studies</t>
+          <t>Specialist in Linguistics</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0009-0008-2733-1586</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6032640</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
@@ -995,39 +995,39 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Khusnul Yaqin, M.Sc.</t>
+          <t>Prof. Dr. Nurhayati Rahman, MS.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>The Aquatic Resources Management Study Program, Faculty of Marine Science and Fisheries, Hasanuddin University</t>
+          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Aquatic Ecotoxicology</t>
+          <t>Specialist in Philological Studies</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-2733-1586</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6002758</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>56263840700</t>
-        </is>
-      </c>
+          <t>6032640</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1040,39 +1040,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Amrullah Amir, S.S., M.A., Ph.D</t>
+          <t>Prof. Dr. Ir. Khusnul Yaqin, M.Sc.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Department of History, Faculty of Cultural Sciences</t>
+          <t>The Aquatic Resources Management Study Program, Faculty of Marine Science and Fisheries, Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Local History of South Sulawesi</t>
+          <t>Specialist in Aquatic Ecotoxicology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9989-7644</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6005379</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
+          <t>6002758</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>56263840700</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1085,30 +1085,38 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Nur, M.A.</t>
+          <t>Amrullah Amir, S.S., M.A., Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Department of Archeology, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of History, Faculty of Cultural Sciences</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Prehistoric Archaeology</t>
+          <t>Specialist in Local History of South Sulawesi</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9989-7644</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6005379</t>
+        </is>
+      </c>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
@@ -1122,38 +1130,30 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Dafirah, M.Hum.</t>
+          <t>Dr. Muhammad Nur, M.A.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of Archeology, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Specialits in Oral Tradition Studies</t>
+          <t>Specialist in Prehistoric Archaeology</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8792-0579</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6024297</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
@@ -1167,30 +1167,38 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Filsah Muslimat, S.S., S.Pd., M. Hum.</t>
+          <t>Dr. Dafirah, M.Hum.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Department of Mandarin Language and Chinese Culture</t>
+          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Linguistics</t>
+          <t>Specialits in Oral Tradition Studies</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8792-0579</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6024297</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
@@ -1204,38 +1212,30 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nurhayati Rahman, MS.</t>
+          <t>Andi Filsah Muslimat, S.S., S.Pd., M. Hum.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of Mandarin Language and Chinese Culture</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Philological Studies</t>
+          <t>Specialist in Linguistics</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0009-0008-2733-1586</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6032640</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
@@ -1249,39 +1249,39 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Khusnul Yaqin, M.Sc.</t>
+          <t>Prof. Dr. Nurhayati Rahman, MS.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>The Aquatic Resources Management Study Program, Faculty of Marine Science and Fisheries, Hasanuddin University</t>
+          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Aquatic Ecotoxicology</t>
+          <t>Specialist in Philological Studies</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-2733-1586</t>
+        </is>
+      </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6002758</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>56263840700</t>
-        </is>
-      </c>
+          <t>6032640</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1294,39 +1294,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Amrullah Amir, S.S., M.A., Ph.D</t>
+          <t>Prof. Dr. Ir. Khusnul Yaqin, M.Sc.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Department of History, Faculty of Cultural Sciences</t>
+          <t>The Aquatic Resources Management Study Program, Faculty of Marine Science and Fisheries, Hasanuddin University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Local History of South Sulawesi</t>
+          <t>Specialist in Aquatic Ecotoxicology</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9989-7644</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>6005379</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="n"/>
+          <t>6002758</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>56263840700</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1339,30 +1339,38 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Nur, M.A.</t>
+          <t>Amrullah Amir, S.S., M.A., Ph.D</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Department of Archeology, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of History, Faculty of Cultural Sciences</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Prehistoric Archaeology</t>
+          <t>Specialist in Local History of South Sulawesi</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9989-7644</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>6005379</t>
+        </is>
+      </c>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
@@ -1376,38 +1384,30 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dr. Dafirah, M.Hum.</t>
+          <t>Dr. Muhammad Nur, M.A.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Department of Archeology, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Specialits in Oral Tradition Studies</t>
+          <t>Specialist in Prehistoric Archaeology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8792-0579</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>6024297</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Pammuda, S.S., M.Hum.</t>
+          <t>Dr. Dafirah, M.Hum.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Cultural Studies</t>
+          <t>Specialits in Oral Tradition Studies</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1445,12 +1445,12 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7312-6689</t>
+          <t>0000-0001-8792-0579</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>6024213</t>
+          <t>6024297</t>
         </is>
       </c>
       <c r="L17" s="12" t="n"/>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Basiah, S.S., M.A</t>
+          <t>Pammuda, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Philological Studies</t>
+          <t>Specialist in Cultural Studies</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1490,12 +1490,12 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3636-7176</t>
+          <t>0000-0002-7312-6689</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>6024279</t>
+          <t>6024213</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
@@ -1511,22 +1511,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nuraidar Agus, S.S., M.Hum.</t>
+          <t>Basiah, S.S., M.A</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Research Center for Language and Literature Preservation, National Research and Innovation Agency (BRIN)</t>
+          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Linguistics Studies</t>
+          <t>Specialist in Philological Studies</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1535,19 +1535,15 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5678-0112</t>
+          <t>0000-0002-3636-7176</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>6025292</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>57718746900</t>
-        </is>
-      </c>
+          <t>6024279</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1560,33 +1556,41 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kathryn Wellen</t>
+          <t>Dr. Nuraidar Agus, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>KITLV/Royal Institute and Caribbean Studies, Netherlands</t>
+          <t>Research Center for Language and Literature Preservation, National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Southeast Asian History</t>
+          <t>Specialist in Linguistics Studies</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5678-0112</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>6025292</t>
+        </is>
+      </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>59890631900</t>
+          <t>57718746900</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -1601,17 +1605,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Dr. Stephen C. Druce</t>
+          <t>Dr. Kathryn Wellen</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Universiti of Brunei Darussalam</t>
+          <t>KITLV/Royal Institute and Caribbean Studies, Netherlands</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1623,15 +1627,11 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4865-1887</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>57193016603</t>
+          <t>59890631900</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -1646,33 +1646,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Prof. C. Campbell Macknight</t>
+          <t>Dr. Stephen C. Druce</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Australian National University (ANU)</t>
+          <t>Universiti of Brunei Darussalam</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Specialist in South Sulawesi History</t>
+          <t>Specialist in Southeast Asian History</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4865-1887</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>57065058800</t>
+          <t>57193016603</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -1687,41 +1691,33 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Jusmianti Garing, S.S.,M.A.</t>
+          <t>Prof. C. Campbell Macknight</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Research Center for Languages, Literature, and Communities, National Research and Innovation Agency (BRIN)</t>
+          <t>Australian National University (ANU)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Theoretical Linguistics Studies</t>
+          <t>Specialist in South Sulawesi History</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5557-8585</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>6038804</t>
-        </is>
-      </c>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>57196374990</t>
+          <t>57065058800</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -1736,22 +1732,22 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Rismawidiawati, S.Sos., M.Si.</t>
+          <t>Jusmianti Garing, S.S.,M.A.</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Research Center for Religious Heritage and Civilization, National Research and Innovation Agency (BRIN)</t>
+          <t>Research Center for Languages, Literature, and Communities, National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Local and Global Historical Studies</t>
+          <t>Specialist in Theoretical Linguistics Studies</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1760,13 +1756,17 @@
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>my-orcid?orcid=0000-0002-1012-7860</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="n"/>
+          <t>0000-0002-5557-8585</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>6038804</t>
+        </is>
+      </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>58728722300</t>
+          <t>57196374990</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Dr. Abd Rahman Hamid</t>
+          <t>Rismawidiawati, S.Sos., M.Si.</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Universitas Islam Negeri Raden Intan Lampung</t>
+          <t>Research Center for Religious Heritage and Civilization, National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Indonesian Maritime History</t>
+          <t>Specialist in Local and Global Historical Studies</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>6745310</t>
-        </is>
-      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0000-0002-1012-7860</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="n"/>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>58729124400</t>
+          <t>58728722300</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Dr Alwi Bin Daud</t>
+          <t>Dr. Abd Rahman Hamid</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Tunku Abdul Rahman University Management and Technology, Malaysia</t>
+          <t>Universitas Islam Negeri Raden Intan Lampung</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Historiography and Malaysian History</t>
+          <t>Specialist in Indonesian Maritime History</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1849,8 +1849,16 @@
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
+      <c r="K26" s="11" t="inlineStr">
+        <is>
+          <t>6745310</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>58729124400</t>
+        </is>
+      </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1863,39 +1871,31 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Ratnawati, S.S.,M.Pd.</t>
+          <t>Dr Alwi Bin Daud</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Research Center for Languages, Literature, and Communities, National Research and Innovation Agency (BRIN)</t>
+          <t>Tunku Abdul Rahman University Management and Technology, Malaysia</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Linguistics Interdiscipliner</t>
+          <t>Specialist in Historiography and Malaysian History</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9518-4575</t>
-        </is>
-      </c>
+      <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>58167923400</t>
-        </is>
-      </c>
+      <c r="L27" s="12" t="n"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1908,22 +1908,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fajar Erikha</t>
+          <t>Ratnawati, S.S.,M.Pd.</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Research Center for Language and Literature Preservation, National Research and Innovation Agency (BRIN)</t>
+          <t>Research Center for Languages, Literature, and Communities, National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Onomastics, Socio-onomastics, Sociolinguistics, Languange and Social Psychology</t>
+          <t>Linguistics Interdiscipliner</t>
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -1932,13 +1932,13 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1713-6281%20</t>
+          <t>0000-0001-9518-4575</t>
         </is>
       </c>
       <c r="K28" s="12" t="n"/>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>57213586562</t>
+          <t>58167923400</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -1953,22 +1953,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Yusuf, S.S.</t>
+          <t>Dr. Fajar Erikha</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>TRG Manuscript and Culture Research Group</t>
+          <t>Research Center for Language and Literature Preservation, National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Applied Linguistics: Toponymy, Onomastics, and Makassarese Manuscript Studies</t>
+          <t>Onomastics, Socio-onomastics, Sociolinguistics, Languange and Social Psychology</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1977,11 +1977,15 @@
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-1969-9117</t>
+          <t>0000-0003-1713-6281%20</t>
         </is>
       </c>
       <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>57213586562</t>
+        </is>
+      </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1994,22 +1998,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Khairil Anwar, S.S., M.A.</t>
+          <t>Yusuf, S.S.</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Department of Japanese Literature, Hasanuddin University</t>
+          <t>TRG Manuscript and Culture Research Group</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Culture and Media studies</t>
+          <t>Applied Linguistics: Toponymy, Onomastics, and Makassarese Manuscript Studies</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -2018,14 +2022,10 @@
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-2171-6140</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>6965834</t>
-        </is>
-      </c>
+          <t>0009-0002-1969-9117</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="n"/>
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="11" t="inlineStr">
         <is>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Ayu Azhariyah, S.E., S.S., Ak., M.A.</t>
+          <t>Khairil Anwar, S.S., M.A.</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Japanese Studies (Anthropology of Education)</t>
+          <t>Culture and Media studies</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -2063,12 +2063,12 @@
       <c r="I31" s="12" t="n"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-1559-0763</t>
+          <t>0009-0009-2171-6140</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>6885701</t>
+          <t>6965834</t>
         </is>
       </c>
       <c r="L31" s="12" t="n"/>
@@ -2084,30 +2084,38 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Nur Amaliah Ramadani, S.S.</t>
+          <t>Ayu Azhariyah, S.E., S.S., Ak., M.A.</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>TRG Manuscript and Culture Research Group</t>
+          <t>Department of Japanese Literature, Hasanuddin University</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Transliteration and Translation of Ancient Bugis Manuscripts, and Manuscript Digitization.</t>
+          <t>Japanese Studies (Anthropology of Education)</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>0009-0002-1559-0763</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>6885701</t>
+        </is>
+      </c>
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="11" t="inlineStr">
         <is>
@@ -2121,33 +2129,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Khaidir Sirajuddin, S.S.</t>
+          <t>Nur Amaliah Ramadani, S.S.</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Museum La Pawawoi Bone</t>
+          <t>TRG Manuscript and Culture Research Group</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Archaeology and Geographic Information Systems (GIS)</t>
+          <t>Transliteration and Translation of Ancient Bugis Manuscripts, and Manuscript Digitization.</t>
         </is>
       </c>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>my-orcid?orcid=0000-0003-0224-3674</t>
-        </is>
-      </c>
+      <c r="J33" s="12" t="n"/>
       <c r="K33" s="12" t="n"/>
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="11" t="inlineStr">
@@ -2162,29 +2166,33 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Amelinda Febrianti, S.S.</t>
+          <t>Khaidir Sirajuddin, S.S.</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>TRG Manuscript and Culture Research Group</t>
+          <t>Museum La Pawawoi Bone</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Stylistics and Literary Studies</t>
+          <t>Archaeology and Geographic Information Systems (GIS)</t>
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>my-orcid?orcid=0000-0003-0224-3674</t>
+        </is>
+      </c>
       <c r="K34" s="12" t="n"/>
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="11" t="inlineStr">
@@ -2199,22 +2207,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Andi Asdar</t>
+          <t>Amelinda Febrianti, S.S.</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Linguitics Department, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>TRG Manuscript and Culture Research Group</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Doctoral in Linguistics</t>
+          <t>Stylistics and Literary Studies</t>
         </is>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -2236,22 +2244,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Alif Aditya</t>
+          <t>Andi Asdar</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+          <t>Linguitics Department, Faculty of Cultural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Undergraduate Student in Local Literature</t>
+          <t>Doctoral in Linguistics</t>
         </is>
       </c>
       <c r="F36" s="12" t="n"/>
@@ -2273,12 +2281,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Pammuda, S.S., M.Hum.</t>
+          <t>Alif Aditya</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2288,23 +2296,15 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Cultural Studies</t>
+          <t>Undergraduate Student in Local Literature</t>
         </is>
       </c>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="12" t="n"/>
       <c r="I37" s="12" t="n"/>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7312-6689</t>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr">
-        <is>
-          <t>6024213</t>
-        </is>
-      </c>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
       <c r="L37" s="12" t="n"/>
       <c r="M37" s="11" t="inlineStr">
         <is>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Basiah, S.S., M.A</t>
+          <t>Pammuda, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Specialist in Philological Studies</t>
+          <t>Specialist in Cultural Studies</t>
         </is>
       </c>
       <c r="F38" s="12" t="n"/>
@@ -2342,12 +2342,12 @@
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3636-7176</t>
+          <t>0000-0002-7312-6689</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
         <is>
-          <t>6024279</t>
+          <t>6024213</t>
         </is>
       </c>
       <c r="L38" s="12" t="n"/>
@@ -2361,18 +2361,46 @@
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="11" t="n"/>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Basiah, S.S., M.A</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Department of Local Literature, Faculty of Cultural Sciences, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>Specialist in Philological Studies</t>
+        </is>
+      </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
       <c r="I39" s="12" t="n"/>
-      <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3636-7176</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>6024279</t>
+        </is>
+      </c>
       <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2561,15 +2589,32 @@
       <c r="L50" s="12" t="n"/>
       <c r="M50" s="12" t="n"/>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="12" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="12" t="n"/>
+      <c r="M51" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
